--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>401515.44</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>363182.88</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>340853.81</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>326143.03</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>300454.31</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>270260.94</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>257931.19</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>250141.44</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>223150.94</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -512,9 +480,6 @@
       </c>
       <c r="B11">
         <v>222723.88</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,95 +391,195 @@
       <c r="B2">
         <v>401515.44</v>
       </c>
+      <c r="C2">
+        <v>356978.81</v>
+      </c>
+      <c r="D2">
+        <v>44536.63</v>
+      </c>
+      <c r="E2">
+        <v>12.47598702006991</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B3">
-        <v>363182.88</v>
+        <v>368403.69</v>
+      </c>
+      <c r="C3">
+        <v>325688.66</v>
+      </c>
+      <c r="D3">
+        <v>42715.03000000003</v>
+      </c>
+      <c r="E3">
+        <v>13.11529544811294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="B4">
-        <v>340853.81</v>
+        <v>363182.88</v>
+      </c>
+      <c r="C4">
+        <v>318189.38</v>
+      </c>
+      <c r="D4">
+        <v>44993.5</v>
+      </c>
+      <c r="E4">
+        <v>14.14047822714888</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B5">
-        <v>326143.03</v>
+        <v>340853.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Cisnes</t>
         </is>
       </c>
       <c r="B6">
-        <v>300454.31</v>
+        <v>326143.03</v>
+      </c>
+      <c r="C6">
+        <v>276420.84</v>
+      </c>
+      <c r="D6">
+        <v>49722.19</v>
+      </c>
+      <c r="E6">
+        <v>17.98785865783492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="B7">
-        <v>270260.94</v>
+        <v>300454.31</v>
+      </c>
+      <c r="C7">
+        <v>248210.28</v>
+      </c>
+      <c r="D7">
+        <v>52244.03</v>
+      </c>
+      <c r="E7">
+        <v>21.04829421247178</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tortel</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="B8">
-        <v>257931.19</v>
+        <v>270260.94</v>
+      </c>
+      <c r="C8">
+        <v>234826.97</v>
+      </c>
+      <c r="D8">
+        <v>35433.97</v>
+      </c>
+      <c r="E8">
+        <v>15.08939539610803</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Tortel</t>
         </is>
       </c>
       <c r="B9">
-        <v>250141.44</v>
+        <v>257931.19</v>
+      </c>
+      <c r="C9">
+        <v>200662.98</v>
+      </c>
+      <c r="D9">
+        <v>57268.20999999999</v>
+      </c>
+      <c r="E9">
+        <v>28.53949941339453</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>Guaitecas</t>
         </is>
       </c>
       <c r="B10">
-        <v>223150.94</v>
+        <v>250141.44</v>
+      </c>
+      <c r="C10">
+        <v>219047.25</v>
+      </c>
+      <c r="D10">
+        <v>31094.19</v>
+      </c>
+      <c r="E10">
+        <v>14.19519761147423</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>223150.94</v>
+      </c>
+      <c r="C11">
+        <v>249556</v>
+      </c>
+      <c r="D11">
+        <v>-26405.06</v>
+      </c>
+      <c r="E11">
+        <v>-10.58081552837839</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Río Ibáñez</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>222723.88</v>
+      </c>
+      <c r="C12">
+        <v>179579.3</v>
+      </c>
+      <c r="D12">
+        <v>43144.58000000002</v>
+      </c>
+      <c r="E12">
+        <v>24.02536372510642</v>
       </c>
     </row>
   </sheetData>
@@ -577,7 +677,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B9">

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_aysen.xlsx
@@ -589,7 +589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -598,20 +598,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>363182.88</v>
+          <t>Río Ibáñez</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -620,88 +612,61 @@
           <t>Chile Chico</t>
         </is>
       </c>
-      <c r="B3">
-        <v>270260.94</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>326143.03</v>
+          <t>Lago Verde</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cochrane</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>300454.31</v>
+          <t>Coyhaique</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>401515.44</v>
+          <t>Cisnes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>250141.44</v>
+          <t>Tortel</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>223150.94</v>
+          <t>O'Higgins</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>340853.81</v>
+          <t>Cochrane</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>222723.88</v>
+          <t>Guaitecas</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tortel</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>257931.19</v>
+          <t>Aysén</t>
+        </is>
       </c>
     </row>
   </sheetData>
